--- a/data/trans_camb/P57_AC_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P57_AC_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,69; -7,73</t>
+          <t>-18,08; -8,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 7,93</t>
+          <t>-1,04; 8,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,78; -11,41</t>
+          <t>-22,2; -10,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,65; -1,18</t>
+          <t>-10,34; -0,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 11,4</t>
+          <t>3,04; 11,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,55; -9,59</t>
+          <t>-18,87; -9,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -6,07</t>
+          <t>-12,58; -5,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,12</t>
+          <t>2,23; 8,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,56; -11,73</t>
+          <t>-19,22; -12,11</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,12; -10,75</t>
+          <t>-23,43; -11,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 10,93</t>
+          <t>-1,31; 11,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,5; -15,7</t>
+          <t>-29,1; -15,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,78; -1,59</t>
+          <t>-13,22; -0,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 15,58</t>
+          <t>3,91; 15,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,91; -13,03</t>
+          <t>-24,06; -12,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -8,15</t>
+          <t>-16,5; -7,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 10,97</t>
+          <t>2,88; 11,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-24,35; -15,82</t>
+          <t>-24,99; -16,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 2,96</t>
+          <t>-5,81; 2,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 13,11</t>
+          <t>4,96; 13,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-41,16; -2,55</t>
+          <t>-42,8; -2,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 4,54</t>
+          <t>-3,27; 4,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 14,17</t>
+          <t>6,35; 14,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,54; -2,48</t>
+          <t>-10,21; -2,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,44</t>
+          <t>-3,69; 2,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 12,63</t>
+          <t>6,9; 12,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-32,55; -3,98</t>
+          <t>-32,07; -4,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 4,48</t>
+          <t>-8,41; 4,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 20,3</t>
+          <t>6,98; 20,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,91; -3,78</t>
+          <t>-61,79; -3,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 6,42</t>
+          <t>-4,37; 6,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,02; 20,21</t>
+          <t>8,4; 19,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,31; -3,59</t>
+          <t>-13,64; -3,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,53</t>
+          <t>-5,11; 3,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 18,35</t>
+          <t>9,63; 18,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,17; -5,82</t>
+          <t>-45,54; -6,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 6,93</t>
+          <t>-3,42; 7,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,88; 26,5</t>
+          <t>17,25; 27,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 7,84</t>
+          <t>-3,6; 8,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 7,45</t>
+          <t>-1,72; 7,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,02; 22,86</t>
+          <t>14,3; 22,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 1,13</t>
+          <t>-12,95; 1,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,98</t>
+          <t>-1,47; 5,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,66; 23,54</t>
+          <t>16,98; 23,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 3,0</t>
+          <t>-6,96; 3,27</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 11,94</t>
+          <t>-5,29; 12,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,01; 45,37</t>
+          <t>26,46; 46,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 13,5</t>
+          <t>-5,69; 13,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 11,87</t>
+          <t>-2,54; 12,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,56; 36,59</t>
+          <t>21,07; 37,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 1,75</t>
+          <t>-19,37; 1,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 9,62</t>
+          <t>-2,22; 9,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,27; 38,34</t>
+          <t>25,84; 38,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 4,71</t>
+          <t>-10,83; 5,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 8,63</t>
+          <t>0,43; 8,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 14,77</t>
+          <t>7,07; 14,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,07; -4,79</t>
+          <t>-13,93; -4,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 13,77</t>
+          <t>6,27; 13,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 13,56</t>
+          <t>6,27; 13,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,84; -7,65</t>
+          <t>-24,44; -7,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,27</t>
+          <t>4,69; 10,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,44; 13,28</t>
+          <t>7,59; 13,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,99; -7,88</t>
+          <t>-18,22; -7,84</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 13,15</t>
+          <t>0,62; 13,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,69; 22,54</t>
+          <t>10,04; 22,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -7,43</t>
+          <t>-20,38; -7,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 20,65</t>
+          <t>8,85; 20,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,08; 20,36</t>
+          <t>8,72; 20,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,22; -11,4</t>
+          <t>-34,56; -11,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,75; 15,43</t>
+          <t>6,79; 15,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,64; 19,87</t>
+          <t>10,77; 19,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,77; -11,67</t>
+          <t>-26,25; -11,59</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,73</t>
+          <t>-3,91; 0,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,18</t>
+          <t>8,92; 13,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,46; -5,9</t>
+          <t>-23,79; -6,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,83</t>
+          <t>0,41; 4,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,4; 13,2</t>
+          <t>9,29; 13,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -6,99</t>
+          <t>-14,02; -6,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,12</t>
+          <t>-1,04; 2,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,61; 12,85</t>
+          <t>9,66; 12,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-17,94; -7,58</t>
+          <t>-17,66; -7,33</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,05</t>
+          <t>-5,69; 0,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12,78; 19,81</t>
+          <t>12,94; 19,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,54; -8,82</t>
+          <t>-34,79; -8,88</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,94</t>
+          <t>0,57; 6,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,07; 18,98</t>
+          <t>12,84; 19,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,4; -10,11</t>
+          <t>-20,05; -9,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,1</t>
+          <t>-1,49; 3,2</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,79</t>
+          <t>13,78; 18,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,11; -10,98</t>
+          <t>-25,31; -10,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_AC_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P57_AC_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-16,74</t>
+          <t>-15,86</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-14,21</t>
+          <t>-13,83</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-15,43</t>
+          <t>-14,81</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -8,12</t>
+          <t>-18,09; -8,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 8,46</t>
+          <t>-1,04; 8,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,2; -10,9</t>
+          <t>-21,04; -10,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -0,14</t>
+          <t>-10,23; -0,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 11,51</t>
+          <t>3,08; 11,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,87; -9,52</t>
+          <t>-18,13; -9,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,58; -5,91</t>
+          <t>-12,75; -5,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 8,37</t>
+          <t>1,99; 8,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-19,22; -12,11</t>
+          <t>-18,56; -11,56</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-22,36%</t>
+          <t>-21,18%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-18,71%</t>
+          <t>-18,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-20,46%</t>
+          <t>-19,63%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,43; -11,06</t>
+          <t>-23,55; -11,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 11,71</t>
+          <t>-1,42; 11,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-29,1; -15,33</t>
+          <t>-27,61; -14,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -0,19</t>
+          <t>-13,08; -0,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 15,73</t>
+          <t>3,95; 15,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,06; -12,67</t>
+          <t>-23,16; -12,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -7,98</t>
+          <t>-16,53; -7,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 11,29</t>
+          <t>2,6; 11,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-24,99; -16,26</t>
+          <t>-24,24; -15,61</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-17,01</t>
+          <t>-2,88</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,59</t>
+          <t>-5,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-12,67</t>
+          <t>-4,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 2,72</t>
+          <t>-6,54; 2,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,54</t>
+          <t>5,09; 13,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-42,8; -2,47</t>
+          <t>-7,76; 1,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 4,3</t>
+          <t>-3,77; 4,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 14,06</t>
+          <t>6,4; 13,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,21; -2,48</t>
+          <t>-9,48; -1,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,26</t>
+          <t>-3,6; 2,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 12,65</t>
+          <t>6,83; 12,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-32,07; -4,21</t>
+          <t>-7,16; -1,2</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-25,18%</t>
+          <t>-4,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-9,06%</t>
+          <t>-7,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,06%</t>
+          <t>-5,85%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 4,14</t>
+          <t>-9,3; 3,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 20,6</t>
+          <t>7,24; 19,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,79; -3,66</t>
+          <t>-11,42; 2,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 6,13</t>
+          <t>-5,03; 6,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,4; 19,78</t>
+          <t>8,63; 19,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,64; -3,54</t>
+          <t>-12,62; -2,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 3,32</t>
+          <t>-4,96; 3,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 18,56</t>
+          <t>9,48; 18,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,54; -6,14</t>
+          <t>-10,01; -1,76</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,01</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>1,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 7,47</t>
+          <t>-3,86; 6,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 27,14</t>
+          <t>17,11; 26,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 8,0</t>
+          <t>-1,88; 9,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 7,81</t>
+          <t>-2,77; 7,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,3; 22,92</t>
+          <t>14,07; 23,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 1,11</t>
+          <t>-5,35; 4,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 5,9</t>
+          <t>-1,16; 6,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,98; 23,53</t>
+          <t>17,0; 23,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 3,27</t>
+          <t>-2,27; 5,25</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-6,16%</t>
+          <t>-0,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-1,43%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 12,78</t>
+          <t>-5,89; 11,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,46; 46,29</t>
+          <t>26,62; 45,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 13,49</t>
+          <t>-2,97; 15,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 12,56</t>
+          <t>-4,13; 12,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,07; 37,17</t>
+          <t>20,64; 37,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 1,61</t>
+          <t>-7,88; 6,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 9,59</t>
+          <t>-1,77; 10,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,84; 38,06</t>
+          <t>26,08; 38,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 5,21</t>
+          <t>-3,52; 8,59</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,25</t>
+          <t>-7,57</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-12,93</t>
+          <t>-7,97</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-11,22</t>
+          <t>-7,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 8,72</t>
+          <t>0,52; 8,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,07; 14,79</t>
+          <t>7,1; 14,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,93; -4,68</t>
+          <t>-11,85; -2,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 13,8</t>
+          <t>6,28; 13,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 13,75</t>
+          <t>5,79; 13,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,44; -7,61</t>
+          <t>-11,92; -3,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,55</t>
+          <t>4,79; 10,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,1</t>
+          <t>7,47; 13,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -7,84</t>
+          <t>-10,61; -4,74</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-13,64%</t>
+          <t>-11,17%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-18,73%</t>
+          <t>-11,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-16,39%</t>
+          <t>-11,37%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 13,4</t>
+          <t>0,79; 13,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,04; 22,47</t>
+          <t>10,22; 22,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,38; -7,2</t>
+          <t>-16,86; -4,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,85; 20,71</t>
+          <t>8,85; 21,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,72; 20,47</t>
+          <t>8,22; 20,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,56; -11,23</t>
+          <t>-16,65; -5,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,79; 15,76</t>
+          <t>6,86; 15,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,77; 19,37</t>
+          <t>10,75; 19,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,25; -11,59</t>
+          <t>-15,25; -7,16</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-11,15</t>
+          <t>-5,53</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-9,66</t>
+          <t>-6,86</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-10,43</t>
+          <t>-6,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,67</t>
+          <t>-3,83; 0,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,3</t>
+          <t>9,16; 13,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-23,79; -6,01</t>
+          <t>-7,98; -3,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,69</t>
+          <t>0,29; 4,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,31</t>
+          <t>9,25; 13,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,02; -6,94</t>
+          <t>-9,14; -4,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,19</t>
+          <t>-1,09; 2,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,66; 12,61</t>
+          <t>9,83; 12,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-17,66; -7,33</t>
+          <t>-7,84; -4,43</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-16,4%</t>
+          <t>-8,14%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-13,66%</t>
+          <t>-9,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,04%</t>
+          <t>-8,94%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,99</t>
+          <t>-5,53; 1,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12,94; 19,95</t>
+          <t>13,23; 20,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,79; -8,88</t>
+          <t>-11,57; -4,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,72</t>
+          <t>0,43; 6,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,84; 19,17</t>
+          <t>12,77; 19,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,05; -9,99</t>
+          <t>-12,69; -7,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,2</t>
+          <t>-1,55; 3,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13,78; 18,44</t>
+          <t>14,05; 18,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -10,62</t>
+          <t>-11,19; -6,47</t>
         </is>
       </c>
     </row>
